--- a/data/trans_orig/P16A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53197</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66735</t>
+          <t>66838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98962</t>
+          <t>98789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99829</t>
+          <t>97510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>140115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440867</t>
+          <t>444192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466381</t>
+          <t>466753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368527</t>
+          <t>368700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>400754</t>
+          <t>400651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>822262</t>
+          <t>821438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>861724</t>
+          <t>864043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50805</t>
+          <t>49936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81388</t>
+          <t>81865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76886</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112128</t>
+          <t>112008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132464</t>
+          <t>133337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179767</t>
+          <t>180387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654101</t>
+          <t>653624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684684</t>
+          <t>685553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513366</t>
+          <t>513486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>548608</t>
+          <t>549480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1181215</t>
+          <t>1180595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1228518</t>
+          <t>1227645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70174</t>
+          <t>67983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104176</t>
+          <t>102953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120785</t>
+          <t>119358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165259</t>
+          <t>163012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202527</t>
+          <t>199674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255735</t>
+          <t>254873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>533473</t>
+          <t>534696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567475</t>
+          <t>569666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524485</t>
+          <t>526732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568959</t>
+          <t>570386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1071659</t>
+          <t>1072521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1124867</t>
+          <t>1127720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63736</t>
+          <t>62446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96037</t>
+          <t>93341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103888</t>
+          <t>103246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141360</t>
+          <t>141927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173606</t>
+          <t>176969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227048</t>
+          <t>229761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>423110</t>
+          <t>425806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>455411</t>
+          <t>456701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>374282</t>
+          <t>373715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411754</t>
+          <t>412396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>807741</t>
+          <t>805028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>861183</t>
+          <t>857820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69724</t>
+          <t>69896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102752</t>
+          <t>101661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99302</t>
+          <t>100373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137388</t>
+          <t>136219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>178237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226727</t>
+          <t>224947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>283958</t>
+          <t>285049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316986</t>
+          <t>316814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>266598</t>
+          <t>267767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>304684</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>563969</t>
+          <t>565749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>612976</t>
+          <t>612459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36865</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62047</t>
+          <t>62536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95747</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127994</t>
+          <t>128599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140575</t>
+          <t>139547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180124</t>
+          <t>180681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230536</t>
+          <t>230047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255718</t>
+          <t>255270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214940</t>
+          <t>214335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247187</t>
+          <t>248012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455393</t>
+          <t>454836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494942</t>
+          <t>495970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43878</t>
+          <t>42989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68550</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119824</t>
+          <t>121052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157708</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171521</t>
+          <t>172445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219262</t>
+          <t>218349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141333</t>
+          <t>142565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166005</t>
+          <t>166894</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>176200</t>
+          <t>175348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>214084</t>
+          <t>212856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>324529</t>
+          <t>325442</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372270</t>
+          <t>371346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>419332</t>
+          <t>419788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>499643</t>
+          <t>494030</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>760960</t>
+          <t>758119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>859025</t>
+          <t>857376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1199751</t>
+          <t>1197256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1327515</t>
+          <t>1327501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2775882</t>
+          <t>2781495</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2856193</t>
+          <t>2855737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2520172</t>
+          <t>2521821</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2618237</t>
+          <t>2621078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5327207</t>
+          <t>5327221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5454971</t>
+          <t>5457466</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>69875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80414</t>
+          <t>80700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113612</t>
+          <t>113484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127552</t>
+          <t>128003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174286</t>
+          <t>174945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383926</t>
+          <t>383230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412776</t>
+          <t>412394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315727</t>
+          <t>315855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348925</t>
+          <t>348639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>708159</t>
+          <t>707500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754893</t>
+          <t>754442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81206</t>
+          <t>83360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119861</t>
+          <t>121204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127024</t>
+          <t>126914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169923</t>
+          <t>171622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221565</t>
+          <t>223018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281206</t>
+          <t>280323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566377</t>
+          <t>565034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>605032</t>
+          <t>602878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439291</t>
+          <t>437592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482190</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1014245</t>
+          <t>1015128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1073886</t>
+          <t>1072433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82617</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121635</t>
+          <t>120087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193248</t>
+          <t>192276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243902</t>
+          <t>242482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286107</t>
+          <t>286968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>350854</t>
+          <t>351615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558419</t>
+          <t>559967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>597437</t>
+          <t>598386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464735</t>
+          <t>466155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515389</t>
+          <t>516361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037837</t>
+          <t>1037076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102584</t>
+          <t>1101723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>83720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120095</t>
+          <t>120993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172936</t>
+          <t>172582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220111</t>
+          <t>222137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268054</t>
+          <t>266648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>328582</t>
+          <t>329574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>494522</t>
+          <t>493624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531675</t>
+          <t>530897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393961</t>
+          <t>391935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441136</t>
+          <t>441490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>900107</t>
+          <t>899115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>960635</t>
+          <t>962041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77121</t>
+          <t>77728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>113317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>141005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181606</t>
+          <t>182455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227855</t>
+          <t>227545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283474</t>
+          <t>283251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315301</t>
+          <t>315027</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>351223</t>
+          <t>350616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>266194</t>
+          <t>265345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310406</t>
+          <t>306795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>592670</t>
+          <t>592893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>648599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66366</t>
+          <t>66151</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101423</t>
+          <t>100213</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>143049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182784</t>
+          <t>178981</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>220411</t>
+          <t>220554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>269923</t>
+          <t>271456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208363</t>
+          <t>209573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243420</t>
+          <t>243635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171212</t>
+          <t>175015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>211716</t>
+          <t>210947</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>393859</t>
+          <t>392326</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443371</t>
+          <t>443228</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63515</t>
+          <t>64468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95346</t>
+          <t>96277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185340</t>
+          <t>187123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>226140</t>
+          <t>225851</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259704</t>
+          <t>257373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311477</t>
+          <t>309074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153690</t>
+          <t>152759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>185521</t>
+          <t>184568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>161796</t>
+          <t>162085</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202596</t>
+          <t>200813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>325495</t>
+          <t>327898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>377268</t>
+          <t>379599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>566113</t>
+          <t>564915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>663418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1129279</t>
+          <t>1134909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1248204</t>
+          <t>1247662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1728497</t>
+          <t>1729485</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1880953</t>
+          <t>1884212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2762790</t>
+          <t>2757761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2855066</t>
+          <t>2856264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2302791</t>
+          <t>2303333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2421716</t>
+          <t>2416086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5091221</t>
+          <t>5087962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5243677</t>
+          <t>5242689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>65799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84793</t>
+          <t>84194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99234</t>
+          <t>99364</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141251</t>
+          <t>139874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355349</t>
+          <t>353664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382146</t>
+          <t>382043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310962</t>
+          <t>311561</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340397</t>
+          <t>341602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673967</t>
+          <t>675344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>715984</t>
+          <t>715854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80315</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116711</t>
+          <t>118764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112137</t>
+          <t>112335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150376</t>
+          <t>152592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205769</t>
+          <t>206058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258991</t>
+          <t>260412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473785</t>
+          <t>471732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510181</t>
+          <t>509131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413168</t>
+          <t>410952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451407</t>
+          <t>451209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>895049</t>
+          <t>893628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>948271</t>
+          <t>947982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97575</t>
+          <t>97656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135648</t>
+          <t>136173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137080</t>
+          <t>136646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180297</t>
+          <t>179736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242736</t>
+          <t>244678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302186</t>
+          <t>306068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>533449</t>
+          <t>532924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571522</t>
+          <t>571441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>481089</t>
+          <t>481650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524306</t>
+          <t>524740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1028297</t>
+          <t>1024415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1087747</t>
+          <t>1085805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106614</t>
+          <t>106121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148798</t>
+          <t>150231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166228</t>
+          <t>163596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>217782</t>
+          <t>212733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284553</t>
+          <t>283572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348988</t>
+          <t>346482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497250</t>
+          <t>495817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>539434</t>
+          <t>539927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431295</t>
+          <t>436344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>482849</t>
+          <t>485481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>946137</t>
+          <t>948643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1010572</t>
+          <t>1011553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90548</t>
+          <t>90661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130350</t>
+          <t>126533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174380</t>
+          <t>173910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220896</t>
+          <t>219091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272318</t>
+          <t>275702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335833</t>
+          <t>336735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347568</t>
+          <t>351385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387370</t>
+          <t>387257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>277758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>322469</t>
+          <t>322939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638934</t>
+          <t>638032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702449</t>
+          <t>699065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46753</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>75111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145375</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183840</t>
+          <t>182842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197737</t>
+          <t>197898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249056</t>
+          <t>247807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259482</t>
+          <t>259219</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287577</t>
+          <t>286998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193922</t>
+          <t>194920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>232387</t>
+          <t>232500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463036</t>
+          <t>464285</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514355</t>
+          <t>514194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>69319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97681</t>
+          <t>95849</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175077</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219497</t>
+          <t>219858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252104</t>
+          <t>247740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307036</t>
+          <t>305717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>161149</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187225</t>
+          <t>187679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180672</t>
+          <t>180311</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>225092</t>
+          <t>224648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>350131</t>
+          <t>351450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>405063</t>
+          <t>409427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,3%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>599790</t>
+          <t>596489</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>685922</t>
+          <t>685443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1043727</t>
+          <t>1045830</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1156043</t>
+          <t>1162104</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1666980</t>
+          <t>1673737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1821371</t>
+          <t>1828832</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2708428</t>
+          <t>2708907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2794560</t>
+          <t>2797861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2388499</t>
+          <t>2382438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2500815</t>
+          <t>2498712</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5117521</t>
+          <t>5110060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5271912</t>
+          <t>5265155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73481</t>
+          <t>76824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82113</t>
+          <t>83656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82105</t>
+          <t>83539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143410</t>
+          <t>142330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326506</t>
+          <t>323163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373203</t>
+          <t>371360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231087</t>
+          <t>229544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269386</t>
+          <t>267777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569777</t>
+          <t>570857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631082</t>
+          <t>629648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>60002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104568</t>
+          <t>103746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58940</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122604</t>
+          <t>122400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135590</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208501</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318979</t>
+          <t>319801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361260</t>
+          <t>363545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388900</t>
+          <t>389104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452564</t>
+          <t>452372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726550</t>
+          <t>723848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799461</t>
+          <t>797343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82264</t>
+          <t>81778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121180</t>
+          <t>120358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150026</t>
+          <t>148316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185725</t>
+          <t>186327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242517</t>
+          <t>242888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297122</t>
+          <t>294243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415158</t>
+          <t>415980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454074</t>
+          <t>454560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356743</t>
+          <t>356141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>392442</t>
+          <t>394152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>781684</t>
+          <t>784563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>836289</t>
+          <t>835918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>71515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234218</t>
+          <t>237873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220578</t>
+          <t>217083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288361</t>
+          <t>286034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257758</t>
+          <t>268114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518345</t>
+          <t>518326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>653568</t>
+          <t>649913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>817968</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424520</t>
+          <t>426847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>492303</t>
+          <t>495798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1082322</t>
+          <t>1082341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1342909</t>
+          <t>1332553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148593</t>
+          <t>148560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188776</t>
+          <t>189691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225941</t>
+          <t>225827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259087</t>
+          <t>259085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>386485</t>
+          <t>384250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>438940</t>
+          <t>439665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372458</t>
+          <t>371543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>412641</t>
+          <t>412674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285800</t>
+          <t>285802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>318946</t>
+          <t>319060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>667181</t>
+          <t>666456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>719636</t>
+          <t>721871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86530</t>
+          <t>87922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113533</t>
+          <t>116070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>314878</t>
+          <t>312339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>525280</t>
+          <t>519100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>387720</t>
+          <t>389747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>726977</t>
+          <t>731105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254632</t>
+          <t>252095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281635</t>
+          <t>280243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>89268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>293490</t>
+          <t>296029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249556</t>
+          <t>245428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>588813</t>
+          <t>586786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99438</t>
+          <t>101458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125997</t>
+          <t>127022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270896</t>
+          <t>271291</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298727</t>
+          <t>299781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>376715</t>
+          <t>379705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>417173</t>
+          <t>418874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156762</t>
+          <t>155737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183321</t>
+          <t>181301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126563</t>
+          <t>125509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154394</t>
+          <t>153999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>290876</t>
+          <t>289175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>331334</t>
+          <t>328344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>602104</t>
+          <t>606557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>855818</t>
+          <t>862316</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1387080</t>
+          <t>1376601</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1944977</t>
+          <t>1886597</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2074461</t>
+          <t>2089193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2778298</t>
+          <t>2761143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2603999</t>
+          <t>2597501</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2857713</t>
+          <t>2853260</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1713621</t>
+          <t>1772001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2271518</t>
+          <t>2281997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4340117</t>
+          <t>4357272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5043954</t>
+          <t>5029222</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66838</t>
+          <t>65442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98789</t>
+          <t>96404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97510</t>
+          <t>102440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140115</t>
+          <t>141754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444192</t>
+          <t>443282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466753</t>
+          <t>466103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368700</t>
+          <t>371085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>400651</t>
+          <t>402047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>821438</t>
+          <t>819799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864043</t>
+          <t>859113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81865</t>
+          <t>79488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76014</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112008</t>
+          <t>111324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>133337</t>
+          <t>133892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180387</t>
+          <t>182093</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>653624</t>
+          <t>656001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685553</t>
+          <t>685459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513486</t>
+          <t>514170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549480</t>
+          <t>551911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1180595</t>
+          <t>1178889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1227645</t>
+          <t>1227090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>69824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102953</t>
+          <t>105944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119358</t>
+          <t>122393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163012</t>
+          <t>163612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>199674</t>
+          <t>199050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254873</t>
+          <t>255951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534696</t>
+          <t>531705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569666</t>
+          <t>567825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526732</t>
+          <t>526132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570386</t>
+          <t>567351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1072521</t>
+          <t>1071443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1127720</t>
+          <t>1128344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62446</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93341</t>
+          <t>95558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103246</t>
+          <t>104712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141927</t>
+          <t>142865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176969</t>
+          <t>175381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229761</t>
+          <t>225503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425806</t>
+          <t>423589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>456701</t>
+          <t>457295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373715</t>
+          <t>372777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412396</t>
+          <t>410930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>805028</t>
+          <t>809286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857820</t>
+          <t>859408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69896</t>
+          <t>70220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101661</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100373</t>
+          <t>97429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136219</t>
+          <t>134192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178237</t>
+          <t>177774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224947</t>
+          <t>225222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>285049</t>
+          <t>283283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316814</t>
+          <t>316490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>267767</t>
+          <t>269794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>306557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>565749</t>
+          <t>565474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>612459</t>
+          <t>612922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37313</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94922</t>
+          <t>96605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>128190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139547</t>
+          <t>138899</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180681</t>
+          <t>180612</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230047</t>
+          <t>229890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255270</t>
+          <t>255467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214335</t>
+          <t>214744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248012</t>
+          <t>246329</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454836</t>
+          <t>454905</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495970</t>
+          <t>496618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67318</t>
+          <t>67569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121052</t>
+          <t>120701</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158560</t>
+          <t>157521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172445</t>
+          <t>171900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>218349</t>
+          <t>220046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142565</t>
+          <t>142314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166894</t>
+          <t>166879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175348</t>
+          <t>176387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212856</t>
+          <t>213207</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>325442</t>
+          <t>323745</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>371346</t>
+          <t>371891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>419788</t>
+          <t>418796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>494030</t>
+          <t>496828</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>758119</t>
+          <t>752583</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>857376</t>
+          <t>853098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1197256</t>
+          <t>1194525</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1327501</t>
+          <t>1326086</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2781495</t>
+          <t>2778697</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2855737</t>
+          <t>2856729</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2521821</t>
+          <t>2526099</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2621078</t>
+          <t>2626614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5327221</t>
+          <t>5328636</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5457466</t>
+          <t>5460197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40711</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69875</t>
+          <t>69855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80700</t>
+          <t>80237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113484</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128003</t>
+          <t>128304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174945</t>
+          <t>175233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383230</t>
+          <t>383250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412394</t>
+          <t>412392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315855</t>
+          <t>315018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348639</t>
+          <t>349102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>707500</t>
+          <t>707212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754442</t>
+          <t>754141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83360</t>
+          <t>84129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121204</t>
+          <t>120822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126914</t>
+          <t>125971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171622</t>
+          <t>170608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223018</t>
+          <t>222545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280323</t>
+          <t>282390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565034</t>
+          <t>565416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>602878</t>
+          <t>602109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>437592</t>
+          <t>438606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482300</t>
+          <t>483243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1015128</t>
+          <t>1013061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1072433</t>
+          <t>1072906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>82598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120087</t>
+          <t>119378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192276</t>
+          <t>193483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>242482</t>
+          <t>245083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286968</t>
+          <t>285895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>351615</t>
+          <t>350845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>559967</t>
+          <t>560676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>598386</t>
+          <t>597456</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>466155</t>
+          <t>463554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516361</t>
+          <t>515154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037076</t>
+          <t>1037846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1101723</t>
+          <t>1102796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83720</t>
+          <t>84500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120993</t>
+          <t>121172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172582</t>
+          <t>170583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222137</t>
+          <t>221791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266648</t>
+          <t>266979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329574</t>
+          <t>328846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493624</t>
+          <t>493445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>530897</t>
+          <t>530117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391935</t>
+          <t>392281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441490</t>
+          <t>443489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>899115</t>
+          <t>899843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>962041</t>
+          <t>961710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77728</t>
+          <t>78962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113317</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141005</t>
+          <t>140522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182455</t>
+          <t>183255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227545</t>
+          <t>229831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283251</t>
+          <t>283932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315027</t>
+          <t>312816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350616</t>
+          <t>349382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>265345</t>
+          <t>264545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>306795</t>
+          <t>307278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>592893</t>
+          <t>592212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>648599</t>
+          <t>646313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66151</t>
+          <t>67707</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100213</t>
+          <t>99453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>143049</t>
+          <t>142457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178981</t>
+          <t>178979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>220554</t>
+          <t>220815</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>271456</t>
+          <t>270264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209573</t>
+          <t>210333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243635</t>
+          <t>242079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175015</t>
+          <t>175017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210947</t>
+          <t>211539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>392326</t>
+          <t>393518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443228</t>
+          <t>442967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>63776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96277</t>
+          <t>94607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187123</t>
+          <t>186114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225851</t>
+          <t>224748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257373</t>
+          <t>257864</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309074</t>
+          <t>310511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152759</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184568</t>
+          <t>185260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162085</t>
+          <t>163188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>200813</t>
+          <t>201822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327898</t>
+          <t>326461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>379599</t>
+          <t>379108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>564915</t>
+          <t>561679</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>663418</t>
+          <t>661042</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1134909</t>
+          <t>1129220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1247662</t>
+          <t>1246793</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1729485</t>
+          <t>1725197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1884212</t>
+          <t>1880104</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2757761</t>
+          <t>2760137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2856264</t>
+          <t>2859500</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2303333</t>
+          <t>2304202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2416086</t>
+          <t>2421775</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5087962</t>
+          <t>5092070</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5242689</t>
+          <t>5246977</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65799</t>
+          <t>66310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>54872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84194</t>
+          <t>82595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99364</t>
+          <t>99676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139874</t>
+          <t>140359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353664</t>
+          <t>353153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382043</t>
+          <t>382407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>311561</t>
+          <t>313160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341602</t>
+          <t>340883</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>675344</t>
+          <t>674859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>715854</t>
+          <t>715542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81365</t>
+          <t>81441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118764</t>
+          <t>118036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112335</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152592</t>
+          <t>151306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206058</t>
+          <t>204662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260412</t>
+          <t>258552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471732</t>
+          <t>472460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509131</t>
+          <t>509055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410952</t>
+          <t>412238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451209</t>
+          <t>451704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>893628</t>
+          <t>895488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>947982</t>
+          <t>949378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>96806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136173</t>
+          <t>136599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136646</t>
+          <t>136597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179736</t>
+          <t>180126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244678</t>
+          <t>246180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306068</t>
+          <t>304488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532924</t>
+          <t>532498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571441</t>
+          <t>572291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>481650</t>
+          <t>481260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524740</t>
+          <t>524789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1024415</t>
+          <t>1025995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1085805</t>
+          <t>1084303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106121</t>
+          <t>105362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150231</t>
+          <t>148233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163596</t>
+          <t>163519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>212733</t>
+          <t>214073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>283572</t>
+          <t>286509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>346482</t>
+          <t>348452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495817</t>
+          <t>497815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>539927</t>
+          <t>540686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>436344</t>
+          <t>435004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>485481</t>
+          <t>485558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>948643</t>
+          <t>946673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1011553</t>
+          <t>1008616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90661</t>
+          <t>91295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126533</t>
+          <t>127611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173910</t>
+          <t>173607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219091</t>
+          <t>219683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>275702</t>
+          <t>276510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>336735</t>
+          <t>332145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>351385</t>
+          <t>350307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387257</t>
+          <t>386623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>277758</t>
+          <t>277166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>322939</t>
+          <t>323242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638032</t>
+          <t>642622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699065</t>
+          <t>698257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75111</t>
+          <t>75407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145262</t>
+          <t>142157</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182842</t>
+          <t>181554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197898</t>
+          <t>197844</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>247807</t>
+          <t>248157</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259219</t>
+          <t>258923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286998</t>
+          <t>288309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>196208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>232500</t>
+          <t>235605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>464285</t>
+          <t>463935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514194</t>
+          <t>514248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>68632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95849</t>
+          <t>96574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175521</t>
+          <t>174394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219858</t>
+          <t>221051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247740</t>
+          <t>254790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>305717</t>
+          <t>307182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>160424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187679</t>
+          <t>188366</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180311</t>
+          <t>179118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>224648</t>
+          <t>225775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>351450</t>
+          <t>349985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>409427</t>
+          <t>402377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>596489</t>
+          <t>595150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>685443</t>
+          <t>688038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1045830</t>
+          <t>1050441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1162104</t>
+          <t>1161428</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1673737</t>
+          <t>1673551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1828832</t>
+          <t>1815264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2708907</t>
+          <t>2706312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2797861</t>
+          <t>2799200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2382438</t>
+          <t>2383114</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2498712</t>
+          <t>2494101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5110060</t>
+          <t>5123628</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5265155</t>
+          <t>5265341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76824</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62773</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45423</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83656</t>
+          <t>98326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109208</t>
+          <t>122523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83539</t>
+          <t>97059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142330</t>
+          <t>156748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>353552</t>
+          <t>360117</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323163</t>
+          <t>336821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>371360</t>
+          <t>378474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>250427</t>
+          <t>287664</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229544</t>
+          <t>264186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267777</t>
+          <t>306682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>603979</t>
+          <t>647782</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>570857</t>
+          <t>613557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>629648</t>
+          <t>673246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80559</t>
+          <t>88636</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60002</t>
+          <t>66012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>113786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>97484</t>
+          <t>103976</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59132</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122400</t>
+          <t>122651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>178043</t>
+          <t>192612</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137708</t>
+          <t>161367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211203</t>
+          <t>225968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>342988</t>
+          <t>388254</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319801</t>
+          <t>363104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363545</t>
+          <t>410878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>414020</t>
+          <t>397107</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389104</t>
+          <t>378432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452372</t>
+          <t>415710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>757008</t>
+          <t>785361</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723848</t>
+          <t>752005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>797343</t>
+          <t>816606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>101343</t>
+          <t>111685</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81778</t>
+          <t>92332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120358</t>
+          <t>133959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166970</t>
+          <t>189333</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148316</t>
+          <t>169434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186327</t>
+          <t>209993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>301019</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242888</t>
+          <t>273781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294243</t>
+          <t>335286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>434995</t>
+          <t>509152</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415980</t>
+          <t>486878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454560</t>
+          <t>528505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>375498</t>
+          <t>432806</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356141</t>
+          <t>412146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>394152</t>
+          <t>452705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>810493</t>
+          <t>941957</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>784563</t>
+          <t>907690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>835918</t>
+          <t>969195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>175859</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71515</t>
+          <t>150941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237873</t>
+          <t>200856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>262044</t>
+          <t>277043</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217083</t>
+          <t>256590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286034</t>
+          <t>297527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>425721</t>
+          <t>452902</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268114</t>
+          <t>422403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518326</t>
+          <t>487329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>724109</t>
+          <t>524758</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>649913</t>
+          <t>499761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>549676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>450837</t>
+          <t>459843</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426847</t>
+          <t>439359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>495798</t>
+          <t>480296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1174946</t>
+          <t>984602</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1082341</t>
+          <t>950175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1332553</t>
+          <t>1015101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>170006</t>
+          <t>182384</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148560</t>
+          <t>161709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189691</t>
+          <t>203282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>242091</t>
+          <t>268976</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225827</t>
+          <t>250285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259085</t>
+          <t>286974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>412097</t>
+          <t>451360</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>384250</t>
+          <t>423383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>439665</t>
+          <t>479657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>391228</t>
+          <t>426962</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371543</t>
+          <t>406064</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>412674</t>
+          <t>447637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>302796</t>
+          <t>338472</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285802</t>
+          <t>320474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319060</t>
+          <t>357163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>694024</t>
+          <t>765434</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>666456</t>
+          <t>737137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>721871</t>
+          <t>793411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106121</t>
+          <t>1216794</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106121</t>
+          <t>1216794</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106121</t>
+          <t>1216794</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>101263</t>
+          <t>109883</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>96519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>125437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>417722</t>
+          <t>231270</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312339</t>
+          <t>216551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>519100</t>
+          <t>246272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>518985</t>
+          <t>341154</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>389747</t>
+          <t>320120</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>731105</t>
+          <t>364926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>266902</t>
+          <t>297197</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252095</t>
+          <t>281643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280243</t>
+          <t>310561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>190646</t>
+          <t>207896</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89268</t>
+          <t>192894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>296029</t>
+          <t>222615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>457548</t>
+          <t>505092</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245428</t>
+          <t>481320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>586786</t>
+          <t>526126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101458</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127022</t>
+          <t>137537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>285297</t>
+          <t>309062</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>271291</t>
+          <t>293625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>299781</t>
+          <t>324008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>398808</t>
+          <t>432266</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>379705</t>
+          <t>411675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>418874</t>
+          <t>454072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>169248</t>
+          <t>186995</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>172661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>181301</t>
+          <t>201708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>139993</t>
+          <t>154944</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125509</t>
+          <t>139998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153999</t>
+          <t>170381</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>309241</t>
+          <t>341938</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>289175</t>
+          <t>320132</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>328344</t>
+          <t>362529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>776794</t>
+          <t>839327</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>606557</t>
+          <t>786469</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>862316</t>
+          <t>898424</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1534383</t>
+          <t>1454508</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1376601</t>
+          <t>1401329</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1886597</t>
+          <t>1502432</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2311177</t>
+          <t>2293836</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2089193</t>
+          <t>2225276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2761143</t>
+          <t>2370307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2683023</t>
+          <t>2693435</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2597501</t>
+          <t>2634338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2853260</t>
+          <t>2746293</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2124215</t>
+          <t>2278733</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1772001</t>
+          <t>2230809</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2281997</t>
+          <t>2331912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4807238</t>
+          <t>4972167</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4357272</t>
+          <t>4895696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5029222</t>
+          <t>5040727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
